--- a/data/trans_camb/P05A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P05A_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,28</t>
+          <t>-8,63</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,45</t>
+          <t>-9,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,71</t>
+          <t>-8,69</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 19,46</t>
+          <t>6,18; 19,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 14,06</t>
+          <t>0,1; 13,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -2,39</t>
+          <t>-14,32; -3,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 17,52</t>
+          <t>1,12; 17,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 15,21</t>
+          <t>-0,16; 15,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -3,46</t>
+          <t>-15,28; -3,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 16,71</t>
+          <t>6,46; 16,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 12,35</t>
+          <t>1,94; 12,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,32; -3,92</t>
+          <t>-12,72; -4,28</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-26,06%</t>
+          <t>-27,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-28,26%</t>
+          <t>-27,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-26,83%</t>
+          <t>-26,8%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,66; 69,87</t>
+          <t>17,68; 69,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 48,39</t>
+          <t>0,4; 45,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,47; -8,07</t>
+          <t>-41,03; -10,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 58,46</t>
+          <t>3,13; 59,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 53,54</t>
+          <t>-0,44; 51,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,71; -11,97</t>
+          <t>-40,57; -10,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,66; 55,05</t>
+          <t>18,18; 55,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 41,02</t>
+          <t>5,24; 40,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,22; -12,6</t>
+          <t>-36,78; -14,59</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-14,23</t>
+          <t>-14,42</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,06</t>
+          <t>-5,49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-9,96</t>
+          <t>-10,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 15,49</t>
+          <t>1,72; 16,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 12,57</t>
+          <t>-1,41; 12,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,15; -7,84</t>
+          <t>-20,17; -8,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 19,08</t>
+          <t>4,26; 18,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 15,48</t>
+          <t>1,75; 15,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 1,0</t>
+          <t>-11,69; 0,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 15,03</t>
+          <t>4,68; 15,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 11,89</t>
+          <t>2,24; 11,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -5,43</t>
+          <t>-14,49; -5,49</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-45,32%</t>
+          <t>-45,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,89%</t>
+          <t>-18,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-32,48%</t>
+          <t>-33,26%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 55,56</t>
+          <t>5,4; 61,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 45,06</t>
+          <t>-3,94; 46,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,91; -28,56</t>
+          <t>-57,82; -30,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 72,27</t>
+          <t>12,13; 69,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 57,23</t>
+          <t>4,55; 60,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 4,35</t>
+          <t>-34,72; 2,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,64; 52,84</t>
+          <t>14,15; 55,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 41,62</t>
+          <t>6,73; 42,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -19,15</t>
+          <t>-43,4; -20,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-15,75</t>
+          <t>-8,44</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,22</t>
+          <t>-17,12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-16,34</t>
+          <t>-10,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 17,46</t>
+          <t>6,1; 17,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 14,02</t>
+          <t>0,93; 12,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,76; -5,89</t>
+          <t>-13,7; -2,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 11,8</t>
+          <t>-7,44; 12,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 8,48</t>
+          <t>-13,75; 7,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,05; -8,05</t>
+          <t>-25,68; -6,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 14,33</t>
+          <t>4,78; 14,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 9,46</t>
+          <t>-0,47; 9,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-27,06; -8,58</t>
+          <t>-14,84; -5,74</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-53,46%</t>
+          <t>-28,65%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-46,08%</t>
+          <t>-45,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-52,12%</t>
+          <t>-33,6%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,64; 66,37</t>
+          <t>18,71; 65,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 54,25</t>
+          <t>2,94; 48,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,97; -20,13</t>
+          <t>-43,19; -10,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 37,54</t>
+          <t>-17,89; 39,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 25,96</t>
+          <t>-31,94; 23,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,05; -25,63</t>
+          <t>-59,85; -22,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,5; 50,23</t>
+          <t>14,39; 50,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 32,37</t>
+          <t>-1,58; 33,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,5; -28,01</t>
+          <t>-44,82; -20,15</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-13,18</t>
+          <t>-13,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>-14,41</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,27</t>
+          <t>-13,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 14,94</t>
+          <t>7,11; 14,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 10,61</t>
+          <t>2,89; 10,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,79; -9,06</t>
+          <t>-16,2; -9,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 10,07</t>
+          <t>-0,74; 9,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 6,53</t>
+          <t>-3,07; 6,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 28,9</t>
+          <t>-18,65; -10,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 11,52</t>
+          <t>5,33; 11,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,95</t>
+          <t>1,84; 7,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 19,7</t>
+          <t>-15,8; -10,35</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-45,29%</t>
+          <t>-44,73%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>-40,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-16,77%</t>
+          <t>-42,01%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,21; 55,75</t>
+          <t>22,9; 55,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,37; 38,94</t>
+          <t>9,12; 37,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,91; -33,41</t>
+          <t>-53,02; -33,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 29,62</t>
+          <t>-1,9; 27,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 19,6</t>
+          <t>-8,1; 20,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 89,66</t>
+          <t>-49,02; -30,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,12; 38,71</t>
+          <t>15,55; 38,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 26,47</t>
+          <t>5,6; 26,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 63,08</t>
+          <t>-48,45; -34,85</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-13,83</t>
+          <t>-13,42</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-21,81</t>
+          <t>-18,3</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-18,8</t>
+          <t>-16,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 8,95</t>
+          <t>-4,29; 8,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 9,2</t>
+          <t>-3,89; 9,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,39; -7,81</t>
+          <t>-19,83; -7,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 3,43</t>
+          <t>-7,33; 3,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 3,66</t>
+          <t>-6,88; 3,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,86; -16,89</t>
+          <t>-23,36; -13,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,66</t>
+          <t>-4,45; 3,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 4,03</t>
+          <t>-4,5; 4,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-23,6; -15,08</t>
+          <t>-20,25; -12,7</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-43,26%</t>
+          <t>-41,95%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-56,89%</t>
+          <t>-47,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-52,36%</t>
+          <t>-45,86%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 32,86</t>
+          <t>-12,04; 31,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 33,15</t>
+          <t>-10,78; 32,63</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,54; -27,05</t>
+          <t>-54,27; -23,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 9,84</t>
+          <t>-17,88; 11,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 11,05</t>
+          <t>-16,76; 9,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,18; -47,63</t>
+          <t>-55,54; -38,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 11,17</t>
+          <t>-11,58; 11,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 12,17</t>
+          <t>-12,02; 12,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-62,16; -44,88</t>
+          <t>-53,22; -38,45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-6,6</t>
+          <t>-5,72</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-18,77</t>
+          <t>-18,65</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-16,32</t>
+          <t>-16,08</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,53; 20,37</t>
+          <t>5,3; 20,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,11; 17,86</t>
+          <t>4,11; 18,53</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 4,3</t>
+          <t>-14,11; 4,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,61</t>
+          <t>4,17; 12,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,18</t>
+          <t>-2,43; 5,44</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-22,38; -15,02</t>
+          <t>-21,96; -14,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,3; 12,56</t>
+          <t>4,87; 12,33</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 6,71</t>
+          <t>-0,56; 6,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-19,69; -12,64</t>
+          <t>-19,43; -12,54</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-28,46%</t>
+          <t>-24,66%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-56,64%</t>
+          <t>-56,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-52,26%</t>
+          <t>-51,52%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19,99; 102,97</t>
+          <t>20,08; 104,92</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14,82; 89,66</t>
+          <t>15,79; 95,66</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-60,21; 22,57</t>
+          <t>-56,02; 25,09</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11,04; 37,6</t>
+          <t>12,02; 38,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 16,34</t>
+          <t>-6,9; 17,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-64,28; -47,67</t>
+          <t>-63,22; -47,13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,2; 43,12</t>
+          <t>15,02; 42,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 22,6</t>
+          <t>-1,71; 23,08</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-60,94; -42,64</t>
+          <t>-60,03; -42,06</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-12,43</t>
+          <t>-11,06</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-10,73</t>
+          <t>-14,29</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-11,53</t>
+          <t>-12,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,87</t>
+          <t>7,92; 12,62</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,66</t>
+          <t>4,0; 9,03</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,61; -10,08</t>
+          <t>-13,08; -8,65</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,1</t>
+          <t>3,36; 7,89</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,66</t>
+          <t>0,02; 4,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 1,43</t>
+          <t>-16,26; -12,16</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,49</t>
+          <t>6,0; 9,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,84</t>
+          <t>2,7; 5,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,69; -3,72</t>
+          <t>-14,13; -11,11</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-42,03%</t>
+          <t>-37,38%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-31,21%</t>
+          <t>-41,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-36,0%</t>
+          <t>-39,63%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>25,21; 45,05</t>
+          <t>25,93; 44,3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13,15; 30,59</t>
+          <t>13,11; 31,96</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,0; -35,15</t>
+          <t>-42,82; -30,23</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,14; 24,7</t>
+          <t>9,48; 23,82</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 14,07</t>
+          <t>0,07; 14,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 4,29</t>
+          <t>-45,95; -36,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,01; 30,55</t>
+          <t>18,12; 30,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,01; 18,81</t>
+          <t>8,09; 18,83</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-45,65; -11,86</t>
+          <t>-42,9; -35,68</t>
         </is>
       </c>
     </row>
